--- a/MSO5000 LCR/Settings/Settings_Custom.xlsx
+++ b/MSO5000 LCR/Settings/Settings_Custom.xlsx
@@ -456,7 +456,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>

--- a/MSO5000 LCR/Settings/Settings_Custom.xlsx
+++ b/MSO5000 LCR/Settings/Settings_Custom.xlsx
@@ -456,7 +456,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
